--- a/www/download/COUNTRY.GRC.rpA1.xlsx
+++ b/www/download/COUNTRY.GRC.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Grécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.679458599438868</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.706339394472836</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.800262461767013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.866003342473462</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.897674167783526</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.06845595822537</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.11656988055068</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1.05752964521951</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.884017000429297</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.803923181967953</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.803793922933501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.796432005396897</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.729660721270685</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.679902072169601</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.716948695892488</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.131</t>
+          <t>0.545626658634859</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>0.483449189278847</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.092</t>
+          <t>0.494057259080913</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>0.554255732267369</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.262</t>
+          <t>0.472179324220149</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>0.403070325026011</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>0.429811188670591</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.356</t>
+          <t>0.268668684730765</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.408</t>
+          <t>0.301658758898478</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.514</t>
+          <t>0.294901700735119</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.551</t>
+          <t>0.341196529025031</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.701</t>
+          <t>0.393199115336014</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.783</t>
+          <t>0.329482890809513</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>0.311534565298447</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.035</t>
+          <t>0.288342544275092</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.406</t>
+          <t>1.92396452327168</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.405</t>
+          <t>1.73263889347557</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>1.77710046611987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>1.79743925690358</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>1.57755764383574</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.595</t>
+          <t>1.41305757398455</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>1.59038164335538</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>1.30612676732449</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>1.37366789084383</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.903</t>
+          <t>1.29508932456718</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>1.35102629926912</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>1.31898672161215</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.17860116442441</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.2176220741379</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>1.16878316842498</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8769.443</t>
+          <t>1.89604151774819</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8633.201</t>
+          <t>1.83428920568902</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8451.014</t>
+          <t>2.03634941073617</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8788.894</t>
+          <t>2.1534630734664</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8982.557</t>
+          <t>2.06477708326113</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9024.035</t>
+          <t>2.0035315099789</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9037.172</t>
+          <t>2.19440228066931</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9187.541</t>
+          <t>1.79132031333849</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9268.693</t>
+          <t>1.42310617820242</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9400.019</t>
+          <t>1.7437777677008</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9491.005</t>
+          <t>1.80510788146435</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10097.279</t>
+          <t>1.68499620109118</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10117.274</t>
+          <t>1.59010208883195</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10032.667</t>
+          <t>1.52533419860636</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10458.883</t>
+          <t>1.4984640283597</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5114.592</t>
+          <t>9821764671.57857</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5050.397</t>
+          <t>10091569699.6901</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4945.373</t>
+          <t>9295043338.24446</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5210.599</t>
+          <t>9252568101.3012</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5317.495</t>
+          <t>9282321016.8407</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5369.195</t>
+          <t>10034817080.6935</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5488.763</t>
+          <t>9542075916.01469</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5677.239</t>
+          <t>9542803697.2875</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5760.728</t>
+          <t>9503953000.05516</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5936.407</t>
+          <t>9301470651.88168</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5983.249</t>
+          <t>9296602047.35015</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6409.294</t>
+          <t>9950659905.84512</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6479.312</t>
+          <t>9991433010.22957</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6512.389</t>
+          <t>10053543009.3824</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6172.579</t>
+          <t>9169763390.06976</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>2070434029.96974</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>2141660867.35594</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>2041249858.33006</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>2105440028.90494</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>2282289258.54912</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>2426240097.25613</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>2354775813.15996</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>2780938664.2284</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>2877402372.49955</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>2964810310.79587</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>2906432174.52813</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>3148040619.319</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>3356986112.49573</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>3408651318.57335</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>3294975569.56148</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>1829008.33129351</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>1813620.87473688</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>1871297.38500624</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>1929869.39749789</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>1897487.99846669</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2220630.9217287</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>2029882.67614171</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>1824056.04638492</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>1450639.27317391</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>1260541.12847616</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>1166783.32387968</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>1159325.03235088</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>1024073.50961539</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>893977.934871889</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>942871.65173663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35826.7145918331</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>35637.2211573768</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>33996.1489061576</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>34534.2760032046</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>36778.2614046945</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>37207.5451397264</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>35762.4141554338</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35826.6452970723</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>38292.9807264599</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>41591.5188137501</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>44369.4879425439</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>48631.3231496409</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>55145.476550363</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>32.67</t>
+          <t>59209.3578152716</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>56954.9702612192</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>76456.6848538078</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>79144.7983101914</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>72429.9241747808</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>71708.330018348</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>74920.8191386037</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>82671.9795521984</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>76545.6301616945</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>78256.483868694</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>83958.9136066708</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>90559.1452732148</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>96935.4904917526</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>108747.485183836</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>123517.75084959</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>137606.25717866</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>117077.641291696</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>1.4702994306531</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>1.35816862322791</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>1.42271831942455</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>1.47482676075342</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>1.32989538878272</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>1.21296951405267</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>1.33090678413009</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>1.04148303989121</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>1.00205856645477</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>1.00228884741245</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>1.05862338589456</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>1.03596296110896</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.930098068288702</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.910547011515887</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>0.873330810104155</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>23188.1171342923</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>25900.4379928804</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>25440.6005235069</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>26326.9602209037</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>28279.773219909</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>26109.0195990388</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>26244.8068278759</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>32235.9102570489</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>40148.5025167437</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>48118.0436104442</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>50696.7558147196</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>52673.3696423062</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>64730.9968994728</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>79534.767314545</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>77802.7010297477</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.679458599438868</t>
+          <t>860.424025304353</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.706339394472836</t>
+          <t>890.396483481169</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.800262461767013</t>
+          <t>849.324995487627</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.866003342473462</t>
+          <t>836.234731044847</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.897674167783526</t>
+          <t>886.799459342024</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06845595822537</t>
+          <t>934.931614268329</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656988055068</t>
+          <t>890.657948038858</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964521951</t>
+          <t>1013.44462309611</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017000429297</t>
+          <t>1028.65362189505</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923181967953</t>
+          <t>1021.31755665777</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793922933501</t>
+          <t>995.897817618169</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432005396897</t>
+          <t>1038.49528965958</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660721270685</t>
+          <t>1079.38794961283</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902072169601</t>
+          <t>1092.58088251786</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695892488</t>
+          <t>1065.98567186921</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-214406833.075151</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1793769.10546049</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-87717120.6094756</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-286147656.447402</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-163613437.921928</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>339395181.164173</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-38756973.8483234</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-38048835.4236421</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>-7502778.79366591</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>564468071.939904</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>667930830.325837</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>857530954.955519</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>747632310.281577</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>685676601.843916</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>227075582.309352</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-90381307.6356611</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>111773115.970608</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>158544170.986337</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-7384522.8049932</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>338155412.089657</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>951741716.433935</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1019726235.37887</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>790813187.40771</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>643661320.43889</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1278999863.61244</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1287787407.13258</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>1275482229.27654</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>1595969737.99932</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1670987817.10047</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>858704671.121923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>-124025525.439489</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>-109979346.865148</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>-246261291.595813</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>-278763133.642409</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>-501768850.011585</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-612346535.269761</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>-1058483209.22719</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-828862022.831352</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>-651164099.232556</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>-714531791.672535</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>-619856576.80674</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>-417951274.321026</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>-848337427.717743</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>-985311215.256552</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>-631629088.812571</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>2125.50497982959</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>2099.70504957776</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>2057.67522571305</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>2069.53609066122</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>2066.14997109599</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>2068.97516009987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>2076.04065342316</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>2068.93000991966</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>2059.42479562971</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>2044.97275336238</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>2050.17853731012</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>2114.33794503303</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>2083.32459648183</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>2087.42713993389</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>1996.94380224218</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>2122.72527551795</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>2098.05777993581</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>2065.18301728827</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>2062.52856445204</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>2107.60881363202</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>2120.75201586986</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>2121.1291237653</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>2108.93477193994</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>2102.6879302526</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>2082.20832119637</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>2085.65960474232</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>2147.98009455787</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>2115.39666869063</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>2028.13928149243</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>2077.32171335532</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>54.56</t>
+          <t>9517.20989534908</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>9875.90258828941</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>11243.1593819634</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>11441.1366680779</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>16562.4641008493</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>17852.1576033361</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>19156.7134472966</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>19530.9315061937</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>25944.0608908084</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>35763.2205205283</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>36377.8948916852</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>43164.5002693218</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>50132.4663304368</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>58538.3917396594</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>45928.476626247</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>192.4</t>
+          <t>698418611.020443</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>717459166.355406</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>177.71</t>
+          <t>733760497.852375</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>741617737.933318</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>157.76</t>
+          <t>850127688.258338</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>141.31</t>
+          <t>1027230017.85156</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>159.04</t>
+          <t>955770243.674547</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>130.61</t>
+          <t>892306013.111031</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>137.37</t>
+          <t>931032172.405463</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>129.51</t>
+          <t>966666257.210033</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>135.1</t>
+          <t>941689231.042555</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>131.9</t>
+          <t>1144309173.84946</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>117.86</t>
+          <t>1115445880.41339</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>121.76</t>
+          <t>1162248587.55384</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>116.88</t>
+          <t>1028120649.1151</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>189.6</t>
+          <t>27379.0023591856</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>183.43</t>
+          <t>29656.0043841906</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>203.63</t>
+          <t>30845.7243839217</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>32574.0740567476</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>206.48</t>
+          <t>37335.6888861809</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>200.35</t>
+          <t>40427.1249225883</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>219.44</t>
+          <t>42303.4920150895</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>179.13</t>
+          <t>46533.9206465096</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>142.31</t>
+          <t>57366.289499536</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>174.38</t>
+          <t>67830.34461642</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>180.51</t>
+          <t>68675.0827026557</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>80437.733576592</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>159.01</t>
+          <t>98724.6647008702</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>152.53</t>
+          <t>115536.132830554</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>149.85</t>
+          <t>89996.0692386105</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8769.443</t>
+          <t>3242188843.43944</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8633.201</t>
+          <t>3651192024.70707</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8451.014</t>
+          <t>3328668674.8875</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8788.894</t>
+          <t>3499765613.66214</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8982.557</t>
+          <t>3746492085.65772</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9024.035</t>
+          <t>4717958014.24143</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9037.172</t>
+          <t>4530314541.97443</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9187.541</t>
+          <t>5022577222.02312</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9268.693</t>
+          <t>5499607051.1071</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9400.019</t>
+          <t>5813541227.18344</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9491.005</t>
+          <t>5607564044.78367</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>10097.279</t>
+          <t>6210110350.49649</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10117.274</t>
+          <t>6700520504.90581</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10032.667</t>
+          <t>6870234531.09749</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10458.883</t>
+          <t>5524620577.71705</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5114.592</t>
+          <t>-17861.7924638365</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5050.397</t>
+          <t>-19780.1017959012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4945.373</t>
+          <t>-19602.5650019583</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5210.599</t>
+          <t>-21132.9373886698</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5317.495</t>
+          <t>-20773.2247853316</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5369.195</t>
+          <t>-22574.9673192522</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5488.763</t>
+          <t>-23146.7785677929</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5677.239</t>
+          <t>-27002.9891403158</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5760.728</t>
+          <t>-31422.2286087276</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5936.407</t>
+          <t>-32067.1240958916</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5983.249</t>
+          <t>-32297.1878109705</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6409.294</t>
+          <t>-37273.2333072702</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6479.312</t>
+          <t>-48592.1983704333</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6512.389</t>
+          <t>-56997.7410908951</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6172.579</t>
+          <t>-44067.5926123636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9821.765</t>
+          <t>-2543770232.419</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10091.57</t>
+          <t>-2933732858.35167</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9295.043</t>
+          <t>-2594908177.03513</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9252.568</t>
+          <t>-2758147875.72882</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9282.321</t>
+          <t>-2896364397.39939</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10034.817</t>
+          <t>-3690727996.38987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9542.076</t>
+          <t>-3574544298.29989</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9542.804</t>
+          <t>-4130271208.91209</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9503.953</t>
+          <t>-4568574878.70164</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9301.471</t>
+          <t>-4846874969.9734</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9296.602</t>
+          <t>-4665874813.74111</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9950.66</t>
+          <t>-5065801176.64703</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9991.433</t>
+          <t>-5585074624.49243</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10053.543</t>
+          <t>-5707985943.54365</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9169.763</t>
+          <t>-4496499928.60195</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>50208.82181</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>51048.6571</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>47709.23426</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>48815.60137</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>50355.49576</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>45772.90765</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>47053.17099</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>50218.51051</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>67831.47736</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>79997.73572</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>86712.20132</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>92843.80953</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>109147.8607</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>121188.13372</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>112371.99438</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4602.365</t>
+          <t>0.107710215711266</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4544.019</t>
+          <t>0.102345594545911</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4362.778</t>
+          <t>0.097288715639229</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4455.978</t>
+          <t>0.0920996050398652</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4556.646</t>
+          <t>0.0764967083446135</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4516.293</t>
+          <t>0.0752339080694597</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4458.095</t>
+          <t>0.078198240037305</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4368.796</t>
+          <t>0.0613470625751352</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4334.676</t>
+          <t>0.0705451310846372</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4271.93</t>
+          <t>0.0712013603936523</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4255.257</t>
+          <t>0.0674462050488443</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4449.885</t>
+          <t>0.067809663644353</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4460.754</t>
+          <t>0.0632153662072067</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4325.849</t>
+          <t>0.0508536906746814</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4460.831</t>
+          <t>0.0411362156697518</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>42013.1707374524</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>43965.1707252105</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>44094.2960000242</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>44965.6765175738</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>47241.814729578</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42409.5159224413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>42875.220364943</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>52357.9240787107</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>67858.6070569255</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>80668.4721738653</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>85337.7830020339</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>92697.5696416739</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>110178.122073115</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>127430.075197121</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>125213.580103711</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2070.434</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2141.661</t>
+          <t>62715.6626402422</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2041.25</t>
+          <t>62295.0916240648</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2105.44</t>
+          <t>63640.3871769388</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2282.289</t>
+          <t>67815.6729060742</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2426.24</t>
+          <t>60970.220312147</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2354.776</t>
+          <t>61799.5299179561</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2780.939</t>
+          <t>74908.7324890371</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2877.402</t>
+          <t>98041.926950747</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2964.81</t>
+          <t>115811.88345511</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2906.432</t>
+          <t>122932.982734002</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3148.041</t>
+          <t>134075.134062603</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3356.986</t>
+          <t>157280.592704313</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3408.651</t>
+          <t>180484.72896841</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3294.976</t>
+          <t>177848.072136483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>147.03</t>
+          <t>335225.885817694</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>135.82</t>
+          <t>356932.075473853</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>142.27</t>
+          <t>346539.195742387</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>147.48</t>
+          <t>352321.394300357</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>132.99</t>
+          <t>368559.8096196</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>340139.918760941</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>133.09</t>
+          <t>351157.720698932</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>104.15</t>
+          <t>397789.440595074</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>100.21</t>
+          <t>515373.910056097</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>100.23</t>
+          <t>607139.36665598</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>105.86</t>
+          <t>646730.500102854</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>703683.416354248</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>93.01</t>
+          <t>824697.360216687</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>950797.044925546</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>926219.70721984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>61487.3810369504</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>64807.0802257089</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>67751.1583199923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>72282.4949672196</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>74965.8991244227</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>75792.6269642812</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.824</t>
+          <t>82742.8481057962</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>86873.6077445838</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>90844.890820531</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>94335.9530956879</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>99751.5252418062</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>103976.826848231</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>110049.14255946</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>113859.387885602</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>42013.1707374524</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>43274.2497793281</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>45783.3205613121</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>47524.1521255572</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>49713.0725772694</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>51407.4949265036</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>51951.26907869</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>56567.0070135727</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>59148.2317585172</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>61118.0189527258</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>63135.5201386857</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>65651.5866472667</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>69587.347001906</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>73141.7950645351</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>75019.8676393409</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>59295.3696077165</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>62430.8634697578</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>59154.9537959352</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>58775.6214830612</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>56473.3854839258</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>51699.0749778529</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>53704.7225620439</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>56639.1239609629</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76505.6225592531</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>91347.1924648905</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>94316.2737359984</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>100389.905417397</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>116864.542535687</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>127886.30613159</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>115903.874663517</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5114592005.43904</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5050397458.99384</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4945373426.299</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5210599326.69538</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5317495219.36193</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5369195369</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5488762918</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5677239118</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5760728069</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5936406620</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5983249244</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6409294101</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6479312411</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6512388590</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6172579253</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8769442990</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8633201448</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8451013902</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8788894157</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8982557105</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9024035231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9037172446</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9187540591</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9268692553</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9400019109</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9491004683</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>10097278528</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10117273801</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10032667395.8805</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10458882644.303</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4602364859.91545</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4544019428.83755</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4362777968.03455</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4455977994.00745</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4556645705.75623</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4516293326</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4458094735</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4368796377</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4334676015</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4271929582</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4255257495</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4449884580</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4460754272</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4325848530.13545</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4460831251.99485</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4131219</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4114854</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4092138</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4261223</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4261966</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4255111</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4260548</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4356484</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4408021</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4514447</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4550601</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4700825</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4782684</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4946734.91482196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5034791.95208993</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2406295</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2405289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2403379</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2517762</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2573625</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2595099</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2643861</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2744046</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2797251</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2902927</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2918404</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3031348</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3110083</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3119816</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3091013</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8769442990</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8633201448</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8451013902</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8788894157</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8982557105</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9024035231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9037172446</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9187540591</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9268692553</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9400019109</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9491004683</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10097278528</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10117273801</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10032667395.8805</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10458882644.303</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5114592005.43904</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5050397458.99384</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4945373426.299</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5210599326.69538</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5317495219.36193</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5369195369</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5488762918</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5677239118</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5760728069</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5936406620</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5983249244</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6409294101</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6479312411</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6512388590</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6172579253</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.225340966083084</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.232948823909172</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.237226927667791</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.24118163639277</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.233904920813957</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.240836708288808</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.238602990085928</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.249243487413833</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232599008054927</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.260788914447732</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.254222469856819</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.263245722347744</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.26784910933332</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.269016670729613</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.269727118190763</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.290971559363126</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.306187083248416</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.328277512911752</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.351647277091884</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.385448066759675</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.399968076680631</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.39776995231038</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.407244687140934</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.395545170131403</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.433181801876958</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.440875469224604</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.399134350888723</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.401697600956369</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404309922144322</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.400615216883796</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.483687474553789</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.460864092842412</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.434495559420457</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.407171086515346</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.380647012426368</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.359195215030561</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.363627057603692</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.343511825445232</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.371855821813671</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.30602928367531</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.304902060918577</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.337619926763533</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.330453289710311</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.326673407126065</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.329657664925441</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.172193539866581</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.17704560351668</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.179749176991545</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.182463532496045</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.175757547097627</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.180077572106593</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.178048293074848</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.185226550922153</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.188413467972605</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.200397403569388</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.199401207613155</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210451308834914</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.216063946478499</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.220359943781744</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.22116539207647</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.355690066285184</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.363197207031498</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.378439299976295</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.393739663077918</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.416540282371946</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.421060563778224</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.418399661683136</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.430252042245956</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.440702665586576</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.458203819898153</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.463184319015617</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.419702690233041</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.420181667462409</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.429839901364051</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.427056382349114</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.472116393848235</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.459757189451821</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.441811523032161</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.423796804426037</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.407702170530427</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.398861864115183</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.403552045242015</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.384521406831891</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.370883866440819</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.341398776532459</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.337414473371228</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.369846000932046</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.363754386059092</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.349800154854205</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.351778225574416</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>213345.15517</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>223447.60162</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>213900.888</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>213400.04529</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>217235.41692</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>202218.87014</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>206975.0654</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>235578.53858</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>303339.46095</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>356814.39674</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>374855.13439</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>407994.35689</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>478252.47301</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>537862.71926</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>489053.61632</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>119108.02389</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>125146.52611</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>121450.04542</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>122416.00866</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>124289.05839</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>112669.29529</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>115504.25248</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>131547.85645</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>174547.54951</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>207159.07592</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>217249.25647</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>234465.03948</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>274145.13524</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>308371.0351</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>293751.9468</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>227772.109671182</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>237366.924976616</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>247726.647313983</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>259588.099334434</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>273162.506765273</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>287944.533978578</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>303214.490316467</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>320489.563175503</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>340228.312234553</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>359268.411014974</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>375676.26822843</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>394358.77688263</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>414661.433611407</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>431763.149905656</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>444746.318180714</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
